--- a/Result/profitability/3529.xlsx
+++ b/Result/profitability/3529.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM73"/>
+  <dimension ref="A1:AM74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,7 +669,7 @@
         <v>0.95</v>
       </c>
       <c r="M2" t="n">
-        <v>5.869999999999999</v>
+        <v>6.1475</v>
       </c>
       <c r="N2" t="n">
         <v>98.24375000000001</v>
@@ -780,7 +780,7 @@
         <v>1.34</v>
       </c>
       <c r="M3" t="n">
-        <v>5.345</v>
+        <v>5.453749999999999</v>
       </c>
       <c r="N3" t="n">
         <v>96.58374999999999</v>
@@ -899,7 +899,7 @@
         <v>0.73</v>
       </c>
       <c r="M4" t="n">
-        <v>4.574999999999999</v>
+        <v>4.7725</v>
       </c>
       <c r="N4" t="n">
         <v>95.38625</v>
@@ -1018,7 +1018,7 @@
         <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>3.855</v>
+        <v>4.154999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>93.94374999999999</v>
@@ -1137,7 +1137,7 @@
         <v>-0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1325</v>
+        <v>3.2875</v>
       </c>
       <c r="N6" t="n">
         <v>91.51625</v>
@@ -1264,7 +1264,7 @@
         <v>0.85</v>
       </c>
       <c r="M7" t="n">
-        <v>2.42375</v>
+        <v>2.45125</v>
       </c>
       <c r="N7" t="n">
         <v>89.4025</v>
@@ -1391,7 +1391,7 @@
         <v>1.26</v>
       </c>
       <c r="M8" t="n">
-        <v>1.63875</v>
+        <v>1.61125</v>
       </c>
       <c r="N8" t="n">
         <v>86.83</v>
@@ -9699,6 +9699,133 @@
       </c>
       <c r="AM73" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1097</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1097</v>
+      </c>
+      <c r="F74" t="n">
+        <v>100</v>
+      </c>
+      <c r="G74" t="n">
+        <v>666</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>60.74%</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>25</v>
+      </c>
+      <c r="J74" t="n">
+        <v>691</v>
+      </c>
+      <c r="K74" t="n">
+        <v>580</v>
+      </c>
+      <c r="L74" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="M74" t="n">
+        <v>6.72125</v>
+      </c>
+      <c r="N74" t="n">
+        <v>100</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
+      </c>
+      <c r="V74" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W74" t="n">
+        <v>-0.2200000000000006</v>
+      </c>
+      <c r="X74" t="n">
+        <v>-0.02756892230576447</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0.4477611940298507</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK74" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
